--- a/NatGas_ETF_Peaks_Troughs.xlsx
+++ b/NatGas_ETF_Peaks_Troughs.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_5752B4CF89BA939366AB024B2830D2BF7F43717D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📊 All Events" sheetId="1" r:id="rId1"/>
@@ -655,10 +655,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -975,7 +975,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="15"/>
@@ -6124,7 +6124,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>146</v>
       </c>
       <c r="B1" s="15"/>
@@ -7065,7 +7065,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>148</v>
       </c>
       <c r="B1" s="15"/>
@@ -7766,7 +7766,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>149</v>
       </c>
       <c r="B1" s="15"/>
@@ -7987,7 +7987,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>150</v>
       </c>
       <c r="B1" s="15"/>
@@ -8228,7 +8228,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>151</v>
       </c>
       <c r="B1" s="15"/>
@@ -9549,7 +9549,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>152</v>
       </c>
       <c r="B1" s="15"/>
